--- a/Result/profitability/2061.xlsx
+++ b/Result/profitability/2061.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>0.26</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1675</v>
+        <v>-0.02625</v>
       </c>
       <c r="N2" t="n">
-        <v>5.6875</v>
+        <v>6.6425</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.46</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.175</v>
+        <v>-0.01749999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>5.7075</v>
+        <v>6.24375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.35</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1525</v>
+        <v>-0.04749999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6825</v>
+        <v>5.271249999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.95</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01999999999999999</v>
+        <v>0.1925</v>
       </c>
       <c r="N5" t="n">
-        <v>5.7525</v>
+        <v>6.29625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.14</v>
       </c>
       <c r="M6" t="n">
-        <v>0.24375</v>
+        <v>0.335</v>
       </c>
       <c r="N6" t="n">
-        <v>6.52125</v>
+        <v>7.21625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.06</v>
       </c>
       <c r="M7" t="n">
-        <v>0.25125</v>
+        <v>0.32875</v>
       </c>
       <c r="N7" t="n">
-        <v>6.9125</v>
+        <v>7.1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0.275</v>
+        <v>0.32875</v>
       </c>
       <c r="N8" t="n">
-        <v>6.51875</v>
+        <v>6.1025</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9586,6 +9586,133 @@
       </c>
       <c r="AM72" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>356</v>
+      </c>
+      <c r="D73" t="n">
+        <v>323</v>
+      </c>
+      <c r="E73" t="n">
+        <v>33</v>
+      </c>
+      <c r="F73" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="G73" t="n">
+        <v>15</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>4.33%</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>29</v>
+      </c>
+      <c r="J73" t="n">
+        <v>44</v>
+      </c>
+      <c r="K73" t="n">
+        <v>42</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-0.10875</v>
+      </c>
+      <c r="N73" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="X73" t="n">
+        <v>1.433333333333334</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>-0.2647058823529412</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>-1.752577319587629</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0.8877551020408161</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
